--- a/Versao 5/ES2N-Requisitos-Funcionais.xlsx
+++ b/Versao 5/ES2N-Requisitos-Funcionais.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
   <si>
     <t xml:space="preserve">LISTA DE REQUISITOS FUNCIONAIS </t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Descrição</t>
   </si>
   <si>
-    <t xml:space="preserve">ATORES (Usuario / Cliente / Lavador / Admin/ Sistema)</t>
+    <t xml:space="preserve">ATORES (Visitante /Usuario / Cliente / Lavador / Admin/ Sistema)</t>
   </si>
   <si>
     <t xml:space="preserve">Prioridade (Alta, Média, Baixa)</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Esse requisito permite cadastrar, alterar ou excluir os dados de um cliente no aplicativo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cliente / Admin</t>
+    <t xml:space="preserve">Cliente </t>
   </si>
   <si>
     <r>
@@ -202,6 +202,9 @@
     <t xml:space="preserve">Esse requisito permite o gerenciamento dos veículos cadastrados por cada cliente.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cliente</t>
+  </si>
+  <si>
     <t xml:space="preserve">RF06</t>
   </si>
   <si>
@@ -220,7 +223,7 @@
     <t xml:space="preserve">Gerenciar Agendamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Esse requisito permite gerenciar a disponibilidade de horários e registrar as reservas dos clientes.</t>
+    <t xml:space="preserve">Esse requisito permite agendar, alterar agendamento e cancelar agendamento</t>
   </si>
   <si>
     <r>
@@ -248,13 +251,22 @@
     <t xml:space="preserve">RF08</t>
   </si>
   <si>
+    <t xml:space="preserve">Gerenciar Horarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esse requisito permite escolher os horarios disponiveis para agendarmento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerenciar Ordem de Serviço</t>
   </si>
   <si>
     <t xml:space="preserve">Esse requisito formaliza a entrada do veículo e acompanha todo o histórico do fluxo de trabalho prestado.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lavador / Admin</t>
+    <t xml:space="preserve">Lavador</t>
   </si>
   <si>
     <r>
@@ -279,7 +291,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">RF09</t>
+    <t xml:space="preserve">RF10</t>
   </si>
   <si>
     <t xml:space="preserve">Gerenciar Produto e Insumo</t>
@@ -288,7 +300,7 @@
     <t xml:space="preserve">Esse requisito mantém o catálogo de produtos disponíveis e monitora os níveis por medição de volume e peso.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF10</t>
+    <t xml:space="preserve">RF11</t>
   </si>
   <si>
     <t xml:space="preserve">Registrar Entrada de Estoque</t>
@@ -297,7 +309,7 @@
     <t xml:space="preserve">Esse requisito permite a inserção manual de informações sobre as novas compras de materiais fornecidas ao sistema.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF11</t>
+    <t xml:space="preserve">RF12</t>
   </si>
   <si>
     <t xml:space="preserve">Calcular Baixa de Estoque</t>
@@ -331,13 +343,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">RF12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processar Pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esse requisito gerencia o processamento de pagamentos físicos e digitais.</t>
+    <t xml:space="preserve">RF13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerenciar Pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esse requisito permite pagar e lançar pagamento</t>
   </si>
   <si>
     <r>
@@ -362,7 +374,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">RF13</t>
+    <t xml:space="preserve">RF14</t>
   </si>
   <si>
     <t xml:space="preserve">Emitir Nota Fiscal Eletrônica</t>
@@ -371,7 +383,10 @@
     <t xml:space="preserve">Esse requisito emite o documento fiscal automaticamente após o processamento financeiro.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF14</t>
+    <t xml:space="preserve">Baixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF15</t>
   </si>
   <si>
     <t xml:space="preserve">Enviar Notificação</t>
@@ -380,7 +395,7 @@
     <t xml:space="preserve">Esse requisito dispara avisos automáticos aos clientes sobre confirmação de agendamentos e conclusão de serviços.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF15</t>
+    <t xml:space="preserve">RF16</t>
   </si>
   <si>
     <t xml:space="preserve">Enviar Alerta de Estoque</t>
@@ -389,7 +404,7 @@
     <t xml:space="preserve">Esse requisito notifica o administrador automaticamente quando os níveis de produtos estiverem baixos.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF16</t>
+    <t xml:space="preserve">RF17</t>
   </si>
   <si>
     <t xml:space="preserve">Gerar Relatório Operacional</t>
@@ -398,7 +413,7 @@
     <t xml:space="preserve">Esse requisito compila e exibe dados sobre os custos operacionais e o consumo de insumos.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF17</t>
+    <t xml:space="preserve">RF18</t>
   </si>
   <si>
     <t xml:space="preserve">Gerar Relatório de Faturamento</t>
@@ -407,40 +422,25 @@
     <t xml:space="preserve">Esse requisito consolida dados financeiros para exibir relatórios de receitas e margens de lucro líquido.</t>
   </si>
   <si>
-    <t xml:space="preserve">RF18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agenda em tempo real</t>
-  </si>
-  <si>
     <t xml:space="preserve">RF19</t>
   </si>
   <si>
+    <t xml:space="preserve">Gerenciar Lavador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esse requisito permite cadastrar, alterar ou excluir os dados de um lavador no aplicativo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerenciar Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">cadastrar/remover/alterar usuarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerenciar Calibração/Configuração de Hardware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">configurar o "fator de conversão" ou tara das balanças no software.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerar relatorio Inadimplencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerar relatorio de todos os cliente inadimplentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerar Pendencias Financeiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS compras serao registradas no sistema???</t>
+    <t xml:space="preserve">Esse requisito permite cadastrar, remover e alterar usuarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitante</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -537,12 +537,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -587,68 +581,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -901,736 +891,717 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="48.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="46.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="48.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="48.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="46.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="2"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" s="2" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="12"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="11" t="s">
+      <c r="D14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="F16" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="F18" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="46.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="46.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="F21" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="33.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="43.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="E23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="43.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="13"/>
+    </row>
+    <row r="28" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="43.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="F28" s="12"/>
+      <c r="G28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="43.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" customFormat="false" ht="27.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" customFormat="false" ht="44.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="8"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="8"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="8"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="8"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="8"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="8"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="8"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="8"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="8"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="8"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="8"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="9"/>
     </row>
     <row r="40" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="8"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="8"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="9"/>
     </row>
     <row r="42" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="8"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="9"/>
     </row>
     <row r="43" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="8"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="8"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="8"/>
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="8"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="8"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="8"/>
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="9"/>
     </row>
     <row r="49" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="8"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="8"/>
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="9"/>
     </row>
     <row r="51" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="8"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="8"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="9"/>
     </row>
     <row r="53" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="8"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="8"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="9"/>
     </row>
     <row r="55" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="8"/>
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="8"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="9"/>
     </row>
     <row r="57" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="8"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="9"/>
     </row>
     <row r="58" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="8"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="9"/>
     </row>
     <row r="59" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="8"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="8"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="9"/>
     </row>
     <row r="61" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="8"/>
-    </row>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="9"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
